--- a/tests/fixtures/vorlesungsverzeichnis_passerelle_fiktiv.xlsx
+++ b/tests/fixtures/vorlesungsverzeichnis_passerelle_fiktiv.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1668,6 +1668,156 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BSc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1. Semester VZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Muster Selina</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ANW7</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ANW7-1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Angewandte Gespraechsfuehrung</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Pflichtmodul</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BSc</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1. Semester VZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Demo Elias</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ANW7</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ANW7-1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Angewandte Gespraechsfuehrung</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Pflichtmodul</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BSc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1. Semester VZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Vorlage Priska</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ANW7</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ANW7-1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Angewandte Gespraechsfuehrung</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Pflichtmodul</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
